--- a/matbench_all_subset_mae_summary.xlsx
+++ b/matbench_all_subset_mae_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>avg_mae</t>
+          <t>avg_score</t>
         </is>
       </c>
     </row>
@@ -508,26 +508,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>all_6_classical_mds_32d_zscore</t>
+          <t>CMDS_32_euc_zscore</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>207.931081</v>
+        <v>197.954321</v>
       </c>
       <c r="D3" t="n">
-        <v>181.628057</v>
+        <v>181.279835</v>
       </c>
       <c r="E3" t="n">
-        <v>176.282158</v>
+        <v>183.70267</v>
       </c>
       <c r="F3" t="n">
-        <v>205.107246</v>
+        <v>205.460391</v>
       </c>
       <c r="G3" t="n">
-        <v>173.956646</v>
+        <v>176.398714</v>
       </c>
       <c r="H3" t="n">
-        <v>188.981038</v>
+        <v>188.959186</v>
       </c>
     </row>
     <row r="4">
@@ -538,26 +538,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>all_6_classical_mds_64d_zscore</t>
+          <t>CMDS_64_euc_zscore</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>208.37163</v>
+        <v>204.153832</v>
       </c>
       <c r="D4" t="n">
-        <v>185.604104</v>
+        <v>181.569866</v>
       </c>
       <c r="E4" t="n">
-        <v>189.993765</v>
+        <v>174.017684</v>
       </c>
       <c r="F4" t="n">
-        <v>202.156708</v>
+        <v>200.619561</v>
       </c>
       <c r="G4" t="n">
-        <v>164.056212</v>
+        <v>170.351666</v>
       </c>
       <c r="H4" t="n">
-        <v>190.036484</v>
+        <v>186.142522</v>
       </c>
     </row>
     <row r="5">
@@ -568,26 +568,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>all_6_mds_32d_zscore</t>
+          <t>MDS_32_euc_zscore</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>199.996475</v>
+        <v>196.129712</v>
       </c>
       <c r="D5" t="n">
-        <v>185.716705</v>
+        <v>183.074286</v>
       </c>
       <c r="E5" t="n">
-        <v>174.392578</v>
+        <v>177.060811</v>
       </c>
       <c r="F5" t="n">
-        <v>203.587943</v>
+        <v>204.552739</v>
       </c>
       <c r="G5" t="n">
-        <v>166.340471</v>
+        <v>164.678507</v>
       </c>
       <c r="H5" t="n">
-        <v>186.006834</v>
+        <v>185.099211</v>
       </c>
     </row>
     <row r="6">
@@ -598,157 +598,157 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>all_6_mds_64d_zscore</t>
+          <t>MDS_64_euc_zscore</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>196.048164</v>
+        <v>216.161697</v>
       </c>
       <c r="D6" t="n">
-        <v>176.204992</v>
+        <v>180.460278</v>
       </c>
       <c r="E6" t="n">
-        <v>173.26466</v>
+        <v>180.573919</v>
       </c>
       <c r="F6" t="n">
-        <v>203.141644</v>
+        <v>201.25136</v>
       </c>
       <c r="G6" t="n">
-        <v>171.961389</v>
+        <v>175.6096</v>
       </c>
       <c r="H6" t="n">
-        <v>184.12417</v>
+        <v>190.811371</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>matbench_steels</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CMDS_32_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>201.314453</v>
+      </c>
+      <c r="D7" t="n">
+        <v>182.411719</v>
+      </c>
+      <c r="E7" t="n">
+        <v>176.598712</v>
+      </c>
+      <c r="F7" t="n">
+        <v>210.79752</v>
+      </c>
+      <c r="G7" t="n">
+        <v>162.547386</v>
+      </c>
+      <c r="H7" t="n">
+        <v>186.733958</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>matbench_expt_gap</t>
+          <t>matbench_steels</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mat2vec</t>
+          <t>CMDS_64_cos_zscore</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.392552</v>
+        <v>205.524821</v>
       </c>
       <c r="D8" t="n">
-        <v>0.420865</v>
+        <v>173.977751</v>
       </c>
       <c r="E8" t="n">
-        <v>0.416612</v>
+        <v>184.157</v>
       </c>
       <c r="F8" t="n">
-        <v>0.441262</v>
+        <v>197.273767</v>
       </c>
       <c r="G8" t="n">
-        <v>0.401034</v>
+        <v>169.472228</v>
       </c>
       <c r="H8" t="n">
-        <v>0.414465</v>
+        <v>186.081113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>matbench_expt_gap</t>
+          <t>matbench_steels</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>all_6_classical_mds_32d_zscore</t>
+          <t>MDS_32_cos_zscore</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.390237</v>
+        <v>208.763953</v>
       </c>
       <c r="D9" t="n">
-        <v>0.395152</v>
+        <v>192.130798</v>
       </c>
       <c r="E9" t="n">
-        <v>0.43515</v>
+        <v>177.998252</v>
       </c>
       <c r="F9" t="n">
-        <v>0.410371</v>
+        <v>194.205118</v>
       </c>
       <c r="G9" t="n">
-        <v>0.396366</v>
+        <v>166.711519</v>
       </c>
       <c r="H9" t="n">
-        <v>0.405455</v>
+        <v>187.961928</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>matbench_expt_gap</t>
+          <t>matbench_steels</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>all_6_classical_mds_64d_zscore</t>
+          <t>MDS_64_cos_zscore</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.396131</v>
+        <v>202.190358</v>
       </c>
       <c r="D10" t="n">
-        <v>0.402698</v>
+        <v>177.95243</v>
       </c>
       <c r="E10" t="n">
-        <v>0.41465</v>
+        <v>173.288734</v>
       </c>
       <c r="F10" t="n">
-        <v>0.423988</v>
+        <v>194.130478</v>
       </c>
       <c r="G10" t="n">
-        <v>0.389723</v>
+        <v>174.882178</v>
       </c>
       <c r="H10" t="n">
-        <v>0.405438</v>
+        <v>184.488836</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>matbench_expt_gap</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>all_6_mds_32d_zscore</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.392033</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.377347</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.422243</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.380961</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.390971</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.392711</v>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -758,37 +758,837 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>all_6_mds_64d_zscore</t>
+          <t>mat2vec</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.367185</v>
+        <v>0.392552</v>
       </c>
       <c r="D12" t="n">
-        <v>0.38933</v>
+        <v>0.420865</v>
       </c>
       <c r="E12" t="n">
-        <v>0.404735</v>
+        <v>0.416612</v>
       </c>
       <c r="F12" t="n">
-        <v>0.398653</v>
+        <v>0.441262</v>
       </c>
       <c r="G12" t="n">
-        <v>0.377495</v>
+        <v>0.401034</v>
       </c>
       <c r="H12" t="n">
-        <v>0.38748</v>
+        <v>0.414465</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>matbench_expt_gap</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CMDS_32_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.411676</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.419209</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.397863</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.40406</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>matbench_expt_gap</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CMDS_64_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.432367</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.456245</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.407097</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.393979</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.419062</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>matbench_expt_gap</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MDS_32_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.382182</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.375558</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.413961</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.370759</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.388889</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.38627</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>matbench_expt_gap</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MDS_64_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.367851</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.382507</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.420888</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.391358</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.351453</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.382811</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>matbench_expt_gap</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CMDS_32_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.396608</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.400045</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.410744</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.406264</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.405084</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>matbench_expt_gap</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CMDS_64_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.409742</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.422269</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.451109</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.409886</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.400323</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.418666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>matbench_expt_gap</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MDS_32_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.375185</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.404125</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.374805</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.381839</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.384753</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>matbench_expt_gap</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MDS_64_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.377536</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.369115</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.416842</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.383066</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.372109</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.383734</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>matbench_expt_is_metal</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>mat2vec</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.96543</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.958911</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.964827</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.951194</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.959068</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.959886</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>matbench_expt_is_metal</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CMDS_32_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.965113</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.961014</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.961861</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.958973</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.960964</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.961585</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>matbench_expt_is_metal</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CMDS_64_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.966453</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.95321</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9508529999999999</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.952202</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.956333</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.95581</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>matbench_expt_is_metal</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MDS_32_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.967912</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.9616</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.962765</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9610919999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9626130000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.9631960000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>matbench_expt_is_metal</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MDS_64_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.966898</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.967607</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.957492</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.962489</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.964618</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.963821</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>matbench_expt_is_metal</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CMDS_32_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.966284</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.959275</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.957149</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.956573</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.955744</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.959005</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>matbench_expt_is_metal</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CMDS_64_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.964631</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.959936</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.952404</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.9564820000000001</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.958244</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.9583390000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>matbench_expt_is_metal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MDS_32_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.970077</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.96548</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.963963</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.960539</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.965044</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.965021</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>matbench_expt_is_metal</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MDS_64_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.966989</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.96315</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.964145</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.961952</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.9625629999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.96376</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>matbench_glass</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>mat2vec</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8811059999999999</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.870742</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.875992</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.872386</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.886532</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.877352</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>matbench_glass</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CMDS_32_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.930698</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.924974</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.91596</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.924735</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.917346</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.922743</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>matbench_glass</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CMDS_64_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.936408</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.922655</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.916089</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.932908</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9193</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.925472</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>matbench_glass</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MDS_32_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.937411</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.915424</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.92131</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.926799</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.924438</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.925076</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>matbench_glass</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MDS_64_euc_zscore</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.9382509999999999</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.9188539999999999</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.916916</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.927967</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.919477</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.924293</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>matbench_glass</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CMDS_32_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.933207</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.918635</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.921087</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.91857</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.920961</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.922492</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>matbench_glass</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CMDS_64_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.935769</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.914627</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.92128</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.928042</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.925146</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.924973</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>matbench_glass</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MDS_32_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.933188</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.911956</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9208</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9246</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.925971</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.923303</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>matbench_glass</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MDS_64_cos_zscore</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.925586</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.913792</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.923123</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.925613</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.927538</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.92313</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
